--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92569365318</v>
+        <v>46157.93101420806</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93101420806</v>
+        <v>46157.93174911038</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93174911038</v>
+        <v>46157.93400975236</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93400975236</v>
+        <v>46157.93718927426</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93718927426</v>
+        <v>46158.2821715252</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2821715252</v>
+        <v>46158.29682734994</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29682734994</v>
+        <v>46158.29815723476</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29815723476</v>
+        <v>46158.33388159353</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33388159353</v>
+        <v>46158.3685797807</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3685797807</v>
+        <v>46158.37288602805</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
